--- a/py project/rocket/generated_data/initial_sets/rocket_initial_n60.xlsx
+++ b/py project/rocket/generated_data/initial_sets/rocket_initial_n60.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>头锥外形参数</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>y</t>
         </is>
       </c>
@@ -499,35 +504,38 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>15.5</v>
+        <v>12.24152906796835</v>
       </c>
       <c r="I2" t="n">
-        <v>3.13</v>
+        <v>2.025297069639855</v>
       </c>
       <c r="J2" t="n">
-        <v>0.96</v>
+        <v>0.6990499190900176</v>
       </c>
       <c r="K2" t="n">
-        <v>48.8</v>
+        <v>31.67203222340607</v>
       </c>
       <c r="L2" t="n">
-        <v>1.89</v>
+        <v>1.89890405852967</v>
       </c>
       <c r="M2" t="n">
-        <v>26.7</v>
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>333.4840163929</v>
       </c>
     </row>
     <row r="3">
@@ -546,35 +554,38 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12.9</v>
+        <v>1.611350017977476</v>
       </c>
       <c r="I3" t="n">
-        <v>2.81</v>
+        <v>4.55847926076019</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.6496448599802103</v>
       </c>
       <c r="K3" t="n">
-        <v>41.3</v>
+        <v>33.48969739783433</v>
       </c>
       <c r="L3" t="n">
-        <v>1.96</v>
+        <v>1.031821349577038</v>
       </c>
       <c r="M3" t="n">
-        <v>130</v>
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.4922644692</v>
       </c>
     </row>
     <row r="4">
@@ -593,35 +604,38 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>2.681149304921599</v>
       </c>
       <c r="I4" t="n">
-        <v>2.06</v>
+        <v>2.290779611794161</v>
       </c>
       <c r="J4" t="n">
-        <v>0.63</v>
+        <v>0.2268163244426703</v>
       </c>
       <c r="K4" t="n">
-        <v>37.4</v>
+        <v>38.63713085818458</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.123160533408008</v>
       </c>
       <c r="M4" t="n">
-        <v>227</v>
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>156.2045590857</v>
       </c>
     </row>
     <row r="5">
@@ -640,35 +654,38 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>18.7321125360489</v>
       </c>
       <c r="I5" t="n">
-        <v>3.97</v>
+        <v>2.37128631478412</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1</v>
+        <v>0.1322105432281156</v>
       </c>
       <c r="K5" t="n">
-        <v>45.6</v>
+        <v>37.98447114806199</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.599847146086241</v>
       </c>
       <c r="M5" t="n">
-        <v>7.59</v>
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>178.1851978493</v>
       </c>
     </row>
     <row r="6">
@@ -687,35 +704,38 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10.7</v>
+        <v>1.970562490111027</v>
       </c>
       <c r="I6" t="n">
-        <v>4.17</v>
+        <v>4.827334310589579</v>
       </c>
       <c r="J6" t="n">
-        <v>0.13</v>
+        <v>0.3000250169819384</v>
       </c>
       <c r="K6" t="n">
-        <v>33.9</v>
+        <v>44.85863245201309</v>
       </c>
       <c r="L6" t="n">
-        <v>1.86</v>
+        <v>1.823813708921951</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.9093923266</v>
       </c>
     </row>
     <row r="7">
@@ -734,35 +754,38 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>18.7</v>
+        <v>9.982131687704907</v>
       </c>
       <c r="I7" t="n">
-        <v>4.81</v>
+        <v>2.701794342029534</v>
       </c>
       <c r="J7" t="n">
-        <v>0.86</v>
+        <v>0.8967928092604589</v>
       </c>
       <c r="K7" t="n">
-        <v>36.7</v>
+        <v>43.70151099155046</v>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>1.45459177173077</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39</v>
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>75.00234222580001</v>
       </c>
     </row>
     <row r="8">
@@ -781,35 +804,38 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>17.9</v>
+        <v>4.914640443352139</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>2.512754780130678</v>
       </c>
       <c r="J8" t="n">
-        <v>0.65</v>
+        <v>0.6757251954551837</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>39.93458216785727</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.679749772739248</v>
       </c>
       <c r="M8" t="n">
-        <v>4.59</v>
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>160.9001518639</v>
       </c>
     </row>
     <row r="9">
@@ -828,35 +854,38 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>9.26429050143042</v>
       </c>
       <c r="I9" t="n">
-        <v>2.39</v>
+        <v>3.356388374871844</v>
       </c>
       <c r="J9" t="n">
-        <v>0.83</v>
+        <v>0.2024703132379644</v>
       </c>
       <c r="K9" t="n">
-        <v>45.5</v>
+        <v>49.41334901592913</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.694758437137681</v>
       </c>
       <c r="M9" t="n">
-        <v>146</v>
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>25.1750664107</v>
       </c>
     </row>
     <row r="10">
@@ -875,35 +904,38 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1.155566847321485</v>
       </c>
       <c r="I10" t="n">
-        <v>4.69</v>
+        <v>2.141167286096068</v>
       </c>
       <c r="J10" t="n">
-        <v>0.67</v>
+        <v>0.2531797971273574</v>
       </c>
       <c r="K10" t="n">
-        <v>32.9</v>
+        <v>49.73192159779655</v>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>1.876727866853058</v>
       </c>
       <c r="M10" t="n">
-        <v>5.65</v>
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>264.7583850653</v>
       </c>
     </row>
     <row r="11">
@@ -922,35 +954,38 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11.1</v>
+        <v>5.973413113800818</v>
       </c>
       <c r="I11" t="n">
-        <v>4.97</v>
+        <v>3.906211394429382</v>
       </c>
       <c r="J11" t="n">
-        <v>0.14</v>
+        <v>0.9854500503740996</v>
       </c>
       <c r="K11" t="n">
-        <v>44.2</v>
+        <v>44.2719516222742</v>
       </c>
       <c r="L11" t="n">
-        <v>1.92</v>
+        <v>1.479271482297664</v>
       </c>
       <c r="M11" t="n">
-        <v>0.64</v>
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9.217345336699999</v>
       </c>
     </row>
     <row r="12">
@@ -969,35 +1004,38 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>15.77095927893132</v>
       </c>
       <c r="I12" t="n">
-        <v>3.99</v>
+        <v>4.73827942963379</v>
       </c>
       <c r="J12" t="n">
-        <v>0.82</v>
+        <v>0.906825653326866</v>
       </c>
       <c r="K12" t="n">
-        <v>40.6</v>
+        <v>39.35521053491868</v>
       </c>
       <c r="L12" t="n">
-        <v>1.98</v>
+        <v>1.303821664043736</v>
       </c>
       <c r="M12" t="n">
-        <v>7.19</v>
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4216895677</v>
       </c>
     </row>
     <row r="13">
@@ -1016,35 +1054,38 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>2.266829564102634</v>
       </c>
       <c r="I13" t="n">
-        <v>2.96</v>
+        <v>4.503716856779866</v>
       </c>
       <c r="J13" t="n">
-        <v>0.24</v>
+        <v>0.7193008975188226</v>
       </c>
       <c r="K13" t="n">
-        <v>42.6</v>
+        <v>46.34880528508816</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.628846741439586</v>
       </c>
       <c r="M13" t="n">
-        <v>6.25</v>
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.9633425758</v>
       </c>
     </row>
     <row r="14">
@@ -1063,35 +1104,38 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>17.3</v>
+        <v>9.525957141952453</v>
       </c>
       <c r="I14" t="n">
-        <v>4.63</v>
+        <v>4.448612869702511</v>
       </c>
       <c r="J14" t="n">
-        <v>0.91</v>
+        <v>0.9335660169948568</v>
       </c>
       <c r="K14" t="n">
-        <v>43.3</v>
+        <v>46.71451537476282</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>1.945967558870274</v>
       </c>
       <c r="M14" t="n">
-        <v>0.27</v>
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.1928581368</v>
       </c>
     </row>
     <row r="15">
@@ -1110,35 +1154,38 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11.2</v>
+        <v>13.68031633275493</v>
       </c>
       <c r="I15" t="n">
-        <v>3.71</v>
+        <v>3.521535642351002</v>
       </c>
       <c r="J15" t="n">
-        <v>0.32</v>
+        <v>0.365973893468139</v>
       </c>
       <c r="K15" t="n">
-        <v>33.5</v>
+        <v>47.91536147452156</v>
       </c>
       <c r="L15" t="n">
-        <v>1.72</v>
+        <v>1.35314403652562</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12.1615751375</v>
       </c>
     </row>
     <row r="16">
@@ -1157,35 +1204,38 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.1</v>
+        <v>5.436893385309792</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>2.789551460666545</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.3711531387566754</v>
       </c>
       <c r="K16" t="n">
-        <v>35.8</v>
+        <v>42.43305325300248</v>
       </c>
       <c r="L16" t="n">
-        <v>1.69</v>
+        <v>1.779935986133439</v>
       </c>
       <c r="M16" t="n">
-        <v>24.6</v>
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>104.6878794835</v>
       </c>
     </row>
     <row r="17">
@@ -1204,35 +1254,38 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15.6</v>
+        <v>0.4107223877452784</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>2.588316160144847</v>
       </c>
       <c r="J17" t="n">
-        <v>0.23</v>
+        <v>0.7942058962932762</v>
       </c>
       <c r="K17" t="n">
-        <v>47.4</v>
+        <v>35.99989950763123</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.286790161912805</v>
       </c>
       <c r="M17" t="n">
-        <v>77.59999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>114.9575181432</v>
       </c>
     </row>
     <row r="18">
@@ -1251,35 +1304,38 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7.5</v>
+        <v>7.216414137554104</v>
       </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>2.216354517135741</v>
       </c>
       <c r="J18" t="n">
-        <v>0.44</v>
+        <v>0.7762845234294715</v>
       </c>
       <c r="K18" t="n">
-        <v>31.5</v>
+        <v>41.06809403343208</v>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>1.071660984818473</v>
       </c>
       <c r="M18" t="n">
-        <v>73.3</v>
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>146.9756656064</v>
       </c>
     </row>
     <row r="19">
@@ -1298,35 +1354,38 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8.800000000000001</v>
+        <v>13.02366480488883</v>
       </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>3.212603912473114</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7</v>
+        <v>0.6304877492190888</v>
       </c>
       <c r="K19" t="n">
-        <v>44.6</v>
+        <v>43.15952159404457</v>
       </c>
       <c r="L19" t="n">
-        <v>1.81</v>
+        <v>1.181883121802268</v>
       </c>
       <c r="M19" t="n">
-        <v>25.9</v>
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>21.3970192168</v>
       </c>
     </row>
     <row r="20">
@@ -1345,35 +1404,38 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>11.20454377748779</v>
       </c>
       <c r="I20" t="n">
-        <v>2.26</v>
+        <v>4.697041062083545</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04</v>
+        <v>0.3466400485306674</v>
       </c>
       <c r="K20" t="n">
-        <v>49.5</v>
+        <v>42.10393634935169</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.926568764297456</v>
       </c>
       <c r="M20" t="n">
-        <v>159</v>
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.7936727943</v>
       </c>
     </row>
     <row r="21">
@@ -1392,35 +1454,38 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.8</v>
+        <v>7.383750944743887</v>
       </c>
       <c r="I21" t="n">
-        <v>4.13</v>
+        <v>4.222358859997923</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.4934106463373594</v>
       </c>
       <c r="K21" t="n">
-        <v>36.1</v>
+        <v>35.10836970244242</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.447612014905485</v>
       </c>
       <c r="M21" t="n">
-        <v>11.8</v>
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>10.6373495518</v>
       </c>
     </row>
     <row r="22">
@@ -1439,35 +1504,38 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>11.9</v>
+        <v>14.8901253652754</v>
       </c>
       <c r="I22" t="n">
-        <v>3.55</v>
+        <v>4.452193475462214</v>
       </c>
       <c r="J22" t="n">
-        <v>0.84</v>
+        <v>0.0715367782872863</v>
       </c>
       <c r="K22" t="n">
-        <v>42</v>
+        <v>31.49147325547246</v>
       </c>
       <c r="L22" t="n">
-        <v>1.74</v>
+        <v>1.966534482688649</v>
       </c>
       <c r="M22" t="n">
-        <v>17.3</v>
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.0822818044</v>
       </c>
     </row>
     <row r="23">
@@ -1486,35 +1554,38 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.6</v>
+        <v>17.08026972209954</v>
       </c>
       <c r="I23" t="n">
-        <v>3.58</v>
+        <v>4.970197456046207</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.7605595359787555</v>
       </c>
       <c r="K23" t="n">
-        <v>37.9</v>
+        <v>32.10949202356466</v>
       </c>
       <c r="L23" t="n">
-        <v>1.06</v>
+        <v>1.014619274862444</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.5852919921</v>
       </c>
     </row>
     <row r="24">
@@ -1533,35 +1604,38 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.9</v>
+        <v>7.806141475851428</v>
       </c>
       <c r="I24" t="n">
-        <v>2.01</v>
+        <v>3.052851477958534</v>
       </c>
       <c r="J24" t="n">
-        <v>0.76</v>
+        <v>0.4627256810781905</v>
       </c>
       <c r="K24" t="n">
-        <v>47.8</v>
+        <v>38.0543786843735</v>
       </c>
       <c r="L24" t="n">
-        <v>1.74</v>
+        <v>1.747506761496613</v>
       </c>
       <c r="M24" t="n">
-        <v>306</v>
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>71.9788000511</v>
       </c>
     </row>
     <row r="25">
@@ -1580,35 +1654,38 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13.4</v>
+        <v>0.7362839284691171</v>
       </c>
       <c r="I25" t="n">
-        <v>2.35</v>
+        <v>4.00386375981916</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1</v>
+        <v>0.1083758870950038</v>
       </c>
       <c r="K25" t="n">
-        <v>39.8</v>
+        <v>40.05717839382745</v>
       </c>
       <c r="L25" t="n">
-        <v>1.22</v>
+        <v>1.234732891922426</v>
       </c>
       <c r="M25" t="n">
-        <v>139</v>
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>10.7838987826</v>
       </c>
     </row>
     <row r="26">
@@ -1627,35 +1704,38 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>8.699999999999999</v>
+        <v>14.01916121702364</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>3.747142369150371</v>
       </c>
       <c r="J26" t="n">
-        <v>0.54</v>
+        <v>0.5510336595340408</v>
       </c>
       <c r="K26" t="n">
-        <v>40.2</v>
+        <v>37.35945429787501</v>
       </c>
       <c r="L26" t="n">
-        <v>1.03</v>
+        <v>1.563983900014777</v>
       </c>
       <c r="M26" t="n">
-        <v>147</v>
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>15.0859541604</v>
       </c>
     </row>
     <row r="27">
@@ -1674,35 +1754,38 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9.9</v>
+        <v>3.041620498218896</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>3.584483819450228</v>
       </c>
       <c r="J27" t="n">
-        <v>0.02</v>
+        <v>0.7350877958217067</v>
       </c>
       <c r="K27" t="n">
-        <v>38.4</v>
+        <v>47.32178923747712</v>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>1.582966846893755</v>
       </c>
       <c r="M27" t="n">
-        <v>262</v>
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>16.9325137571</v>
       </c>
     </row>
     <row r="28">
@@ -1721,35 +1804,38 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>14.2</v>
+        <v>5.225546737611907</v>
       </c>
       <c r="I28" t="n">
-        <v>2.91</v>
+        <v>3.826955894153059</v>
       </c>
       <c r="J28" t="n">
-        <v>0.28</v>
+        <v>0.05617274257552857</v>
       </c>
       <c r="K28" t="n">
-        <v>38.6</v>
+        <v>45.96761592845294</v>
       </c>
       <c r="L28" t="n">
-        <v>1.86</v>
+        <v>1.267967874256794</v>
       </c>
       <c r="M28" t="n">
-        <v>87.5</v>
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>9.8345394799</v>
       </c>
     </row>
     <row r="29">
@@ -1768,35 +1854,38 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>16.6</v>
+        <v>19.89322705840269</v>
       </c>
       <c r="I29" t="n">
-        <v>2.71</v>
+        <v>3.024986691576386</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9</v>
+        <v>0.5936966417050361</v>
       </c>
       <c r="K29" t="n">
-        <v>40.9</v>
+        <v>33.10515209665767</v>
       </c>
       <c r="L29" t="n">
-        <v>1.38</v>
+        <v>1.733036700439962</v>
       </c>
       <c r="M29" t="n">
-        <v>50.5</v>
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>52.5904674637</v>
       </c>
     </row>
     <row r="30">
@@ -1815,35 +1904,38 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>17.2</v>
+        <v>11.79900520467093</v>
       </c>
       <c r="I30" t="n">
-        <v>3.32</v>
+        <v>2.696084664928723</v>
       </c>
       <c r="J30" t="n">
-        <v>0.44</v>
+        <v>0.9569864894930554</v>
       </c>
       <c r="K30" t="n">
-        <v>30.8</v>
+        <v>34.08926239889927</v>
       </c>
       <c r="L30" t="n">
-        <v>1.14</v>
+        <v>1.085216640763489</v>
       </c>
       <c r="M30" t="n">
-        <v>33.6</v>
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>68.46592814349999</v>
       </c>
     </row>
     <row r="31">
@@ -1862,35 +1954,38 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5.2</v>
+        <v>0.05730681971644409</v>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>3.676979238612238</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0.9168717614591212</v>
       </c>
       <c r="K31" t="n">
-        <v>32</v>
+        <v>41.7560533571044</v>
       </c>
       <c r="L31" t="n">
-        <v>1.54</v>
+        <v>1.500225128052693</v>
       </c>
       <c r="M31" t="n">
-        <v>9.25</v>
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>19.9222593723</v>
       </c>
     </row>
     <row r="32">
@@ -1909,35 +2004,38 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>12.5</v>
+        <v>13.66514827705354</v>
       </c>
       <c r="I32" t="n">
-        <v>4.35</v>
+        <v>3.171089473444495</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3</v>
+        <v>0.02906662509295534</v>
       </c>
       <c r="K32" t="n">
-        <v>44.9</v>
+        <v>40.34850217081608</v>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>1.102498061702525</v>
       </c>
       <c r="M32" t="n">
-        <v>2.6</v>
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>38.3299832525</v>
       </c>
     </row>
     <row r="33">
@@ -1956,35 +2054,38 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4.8</v>
+        <v>2.55104225000655</v>
       </c>
       <c r="I33" t="n">
-        <v>3.65</v>
+        <v>4.788491141369303</v>
       </c>
       <c r="J33" t="n">
-        <v>0.62</v>
+        <v>0.7161598189816699</v>
       </c>
       <c r="K33" t="n">
-        <v>35.2</v>
+        <v>30.8527691326474</v>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>1.038983426312606</v>
       </c>
       <c r="M33" t="n">
-        <v>25.5</v>
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5.6006221212</v>
       </c>
     </row>
     <row r="34">
@@ -2003,35 +2104,38 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3.9</v>
+        <v>16.69708903776882</v>
       </c>
       <c r="I34" t="n">
-        <v>3.07</v>
+        <v>4.156371679128763</v>
       </c>
       <c r="J34" t="n">
-        <v>0.38</v>
+        <v>0.8340019692489942</v>
       </c>
       <c r="K34" t="n">
-        <v>42.3</v>
+        <v>33.81551425569021</v>
       </c>
       <c r="L34" t="n">
-        <v>1.97</v>
+        <v>1.396149779375531</v>
       </c>
       <c r="M34" t="n">
-        <v>79.2</v>
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>6.0213680109</v>
       </c>
     </row>
     <row r="35">
@@ -2050,35 +2154,38 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.1</v>
+        <v>18.07913588429678</v>
       </c>
       <c r="I35" t="n">
-        <v>3.26</v>
+        <v>2.64476321109364</v>
       </c>
       <c r="J35" t="n">
-        <v>0.46</v>
+        <v>0.6041123540671099</v>
       </c>
       <c r="K35" t="n">
-        <v>35.5</v>
+        <v>44.53385675052391</v>
       </c>
       <c r="L35" t="n">
-        <v>1.83</v>
+        <v>1.326329968129479</v>
       </c>
       <c r="M35" t="n">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>52.2208325043</v>
       </c>
     </row>
     <row r="36">
@@ -2097,35 +2204,38 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6.3</v>
+        <v>6.791675118443992</v>
       </c>
       <c r="I36" t="n">
-        <v>4.74</v>
+        <v>4.259673771953611</v>
       </c>
       <c r="J36" t="n">
-        <v>0.19</v>
+        <v>0.2437459096885867</v>
       </c>
       <c r="K36" t="n">
-        <v>39</v>
+        <v>34.81752772876622</v>
       </c>
       <c r="L36" t="n">
-        <v>1.77</v>
+        <v>1.416682198893857</v>
       </c>
       <c r="M36" t="n">
-        <v>1.03</v>
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>11.0246502077</v>
       </c>
     </row>
     <row r="37">
@@ -2144,35 +2254,38 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>13.9</v>
+        <v>17.71449995737024</v>
       </c>
       <c r="I37" t="n">
-        <v>4.05</v>
+        <v>4.121548543010356</v>
       </c>
       <c r="J37" t="n">
-        <v>0.06</v>
+        <v>0.4813822979767295</v>
       </c>
       <c r="K37" t="n">
-        <v>30.7</v>
+        <v>32.78370526513611</v>
       </c>
       <c r="L37" t="n">
-        <v>1.9</v>
+        <v>1.65787295366159</v>
       </c>
       <c r="M37" t="n">
-        <v>1.12</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>10.8182682644</v>
       </c>
     </row>
     <row r="38">
@@ -2191,35 +2304,38 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>16.3</v>
+        <v>4.350343840649603</v>
       </c>
       <c r="I38" t="n">
-        <v>4.32</v>
+        <v>3.971806860868597</v>
       </c>
       <c r="J38" t="n">
-        <v>0.37</v>
+        <v>0.5688217198003515</v>
       </c>
       <c r="K38" t="n">
-        <v>34.3</v>
+        <v>41.43505514785829</v>
       </c>
       <c r="L38" t="n">
-        <v>1.11</v>
+        <v>1.526666604927275</v>
       </c>
       <c r="M38" t="n">
-        <v>1.07</v>
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>11.25823144</v>
       </c>
     </row>
     <row r="39">
@@ -2238,35 +2354,38 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3.5</v>
+        <v>15.26250031249126</v>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>2.877940416389934</v>
       </c>
       <c r="J39" t="n">
-        <v>0.21</v>
+        <v>0.2692677354498603</v>
       </c>
       <c r="K39" t="n">
-        <v>37.2</v>
+        <v>42.79232471308864</v>
       </c>
       <c r="L39" t="n">
-        <v>1.65</v>
+        <v>1.368404935338466</v>
       </c>
       <c r="M39" t="n">
-        <v>2.72</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>50.8816104548</v>
       </c>
     </row>
     <row r="40">
@@ -2285,35 +2404,38 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.7</v>
+        <v>17.54674491939355</v>
       </c>
       <c r="I40" t="n">
-        <v>4.85</v>
+        <v>4.063895861895466</v>
       </c>
       <c r="J40" t="n">
-        <v>0.34</v>
+        <v>0.8228829323065631</v>
       </c>
       <c r="K40" t="n">
-        <v>42.9</v>
+        <v>30.44873540611124</v>
       </c>
       <c r="L40" t="n">
-        <v>1.43</v>
+        <v>1.601938277509828</v>
       </c>
       <c r="M40" t="n">
-        <v>0.793</v>
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>10.290373873</v>
       </c>
     </row>
     <row r="41">
@@ -2332,35 +2454,38 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>19.4</v>
+        <v>6.07758497440302</v>
       </c>
       <c r="I41" t="n">
-        <v>2.74</v>
+        <v>3.763050594409551</v>
       </c>
       <c r="J41" t="n">
-        <v>0.92</v>
+        <v>0.4340489221167759</v>
       </c>
       <c r="K41" t="n">
-        <v>46.3</v>
+        <v>39.29361061289685</v>
       </c>
       <c r="L41" t="n">
-        <v>1.1</v>
+        <v>1.985946642097955</v>
       </c>
       <c r="M41" t="n">
-        <v>29.5</v>
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>25.5733047936</v>
       </c>
     </row>
     <row r="42">
@@ -2379,35 +2504,38 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>9.9</v>
+        <v>3.537329936722331</v>
       </c>
       <c r="I42" t="n">
-        <v>2.61</v>
+        <v>2.338016071193156</v>
       </c>
       <c r="J42" t="n">
-        <v>0.52</v>
+        <v>0.8024441126142783</v>
       </c>
       <c r="K42" t="n">
-        <v>32.8</v>
+        <v>35.53872736517273</v>
       </c>
       <c r="L42" t="n">
-        <v>1.18</v>
+        <v>1.645813367641938</v>
       </c>
       <c r="M42" t="n">
-        <v>109</v>
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>228.3054548732</v>
       </c>
     </row>
     <row r="43">
@@ -2426,35 +2554,38 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>9.300000000000001</v>
+        <v>6.367812577408952</v>
       </c>
       <c r="I43" t="n">
-        <v>4.54</v>
+        <v>2.942151246949938</v>
       </c>
       <c r="J43" t="n">
-        <v>0.28</v>
+        <v>0.8634825026926598</v>
       </c>
       <c r="K43" t="n">
-        <v>30</v>
+        <v>49.0914565219503</v>
       </c>
       <c r="L43" t="n">
-        <v>1.79</v>
+        <v>1.841708149610698</v>
       </c>
       <c r="M43" t="n">
-        <v>1.05</v>
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>63.3783542007</v>
       </c>
     </row>
     <row r="44">
@@ -2473,35 +2604,38 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>7.7</v>
+        <v>18.64288571289659</v>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>4.922320553201396</v>
       </c>
       <c r="J44" t="n">
-        <v>0.77</v>
+        <v>0.1716967160364511</v>
       </c>
       <c r="K44" t="n">
-        <v>49.7</v>
+        <v>32.61312660544141</v>
       </c>
       <c r="L44" t="n">
-        <v>1.67</v>
+        <v>1.166204404346314</v>
       </c>
       <c r="M44" t="n">
-        <v>20.1</v>
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.0294902058</v>
       </c>
     </row>
     <row r="45">
@@ -2520,35 +2654,38 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>19.7</v>
+        <v>8.29533254396404</v>
       </c>
       <c r="I45" t="n">
-        <v>2.59</v>
+        <v>2.961069877596751</v>
       </c>
       <c r="J45" t="n">
-        <v>0.97</v>
+        <v>0.5297598017011337</v>
       </c>
       <c r="K45" t="n">
-        <v>39.5</v>
+        <v>36.03568883358382</v>
       </c>
       <c r="L45" t="n">
-        <v>1.42</v>
+        <v>1.763270062156751</v>
       </c>
       <c r="M45" t="n">
-        <v>59.8</v>
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>89.1976306279</v>
       </c>
     </row>
     <row r="46">
@@ -2567,35 +2704,38 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4.8</v>
+        <v>12.72854548975132</v>
       </c>
       <c r="I46" t="n">
-        <v>2.47</v>
+        <v>4.8577996443092</v>
       </c>
       <c r="J46" t="n">
-        <v>0.16</v>
+        <v>0.4149959096815065</v>
       </c>
       <c r="K46" t="n">
-        <v>43.9</v>
+        <v>47.60593499177352</v>
       </c>
       <c r="L46" t="n">
-        <v>1.6</v>
+        <v>1.406476735503541</v>
       </c>
       <c r="M46" t="n">
-        <v>149</v>
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.2355936119</v>
       </c>
     </row>
     <row r="47">
@@ -2614,35 +2754,38 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.1</v>
+        <v>19.64298075556521</v>
       </c>
       <c r="I47" t="n">
-        <v>3.36</v>
+        <v>3.107086086164084</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6</v>
+        <v>0.5405582416613934</v>
       </c>
       <c r="K47" t="n">
-        <v>49</v>
+        <v>37.32425071953371</v>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.711239213917697</v>
       </c>
       <c r="M47" t="n">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>40.1171629241</v>
       </c>
     </row>
     <row r="48">
@@ -2661,35 +2804,38 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5.9</v>
+        <v>10.67957513841275</v>
       </c>
       <c r="I48" t="n">
-        <v>3.87</v>
+        <v>2.470330800172544</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6589165559961115</v>
       </c>
       <c r="K48" t="n">
-        <v>32.4</v>
+        <v>45.11410329343668</v>
       </c>
       <c r="L48" t="n">
-        <v>1.29</v>
+        <v>1.341227673734436</v>
       </c>
       <c r="M48" t="n">
-        <v>21.5</v>
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>87.1282079838</v>
       </c>
     </row>
     <row r="49">
@@ -2708,35 +2854,38 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.2</v>
+        <v>15.51880346131344</v>
       </c>
       <c r="I49" t="n">
-        <v>4.45</v>
+        <v>3.278693517364578</v>
       </c>
       <c r="J49" t="n">
-        <v>0.71</v>
+        <v>0.1508495002446572</v>
       </c>
       <c r="K49" t="n">
-        <v>48.3</v>
+        <v>48.82327533854718</v>
       </c>
       <c r="L49" t="n">
-        <v>1.26</v>
+        <v>1.189282577356893</v>
       </c>
       <c r="M49" t="n">
-        <v>1.07</v>
+        <v>1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>19.1807273976</v>
       </c>
     </row>
     <row r="50">
@@ -2755,35 +2904,38 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>14.7</v>
+        <v>8.531620868742987</v>
       </c>
       <c r="I50" t="n">
-        <v>4.26</v>
+        <v>3.301778607365845</v>
       </c>
       <c r="J50" t="n">
-        <v>0.73</v>
+        <v>0.8794757061014147</v>
       </c>
       <c r="K50" t="n">
-        <v>46.5</v>
+        <v>36.72919727073084</v>
       </c>
       <c r="L50" t="n">
-        <v>1.06</v>
+        <v>1.865451829541312</v>
       </c>
       <c r="M50" t="n">
-        <v>0.777</v>
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>50.9941384557</v>
       </c>
     </row>
     <row r="51">
@@ -2802,35 +2954,38 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>12.3</v>
+        <v>10.56921144005339</v>
       </c>
       <c r="I51" t="n">
-        <v>2.87</v>
+        <v>4.335140648010748</v>
       </c>
       <c r="J51" t="n">
-        <v>0.41</v>
+        <v>0.09507051162767199</v>
       </c>
       <c r="K51" t="n">
-        <v>34.5</v>
+        <v>45.4750236212646</v>
       </c>
       <c r="L51" t="n">
-        <v>1.63</v>
+        <v>1.907597126198062</v>
       </c>
       <c r="M51" t="n">
-        <v>84.3</v>
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.0531540034</v>
       </c>
     </row>
     <row r="52">
@@ -2849,35 +3004,38 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.4</v>
+        <v>8.825481359507624</v>
       </c>
       <c r="I52" t="n">
-        <v>4.31</v>
+        <v>3.41910336769622</v>
       </c>
       <c r="J52" t="n">
-        <v>0.73</v>
+        <v>0.3267007911742124</v>
       </c>
       <c r="K52" t="n">
-        <v>44.6</v>
+        <v>43.35375860713182</v>
       </c>
       <c r="L52" t="n">
-        <v>1.16</v>
+        <v>1.0558266520641</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>18.9517931059</v>
       </c>
     </row>
     <row r="53">
@@ -2896,35 +3054,38 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2.3</v>
+        <v>12.62919272890968</v>
       </c>
       <c r="I53" t="n">
-        <v>2.26</v>
+        <v>3.641173839236674</v>
       </c>
       <c r="J53" t="n">
-        <v>0.63</v>
+        <v>0.5115003962298157</v>
       </c>
       <c r="K53" t="n">
-        <v>47.4</v>
+        <v>31.0756999604029</v>
       </c>
       <c r="L53" t="n">
-        <v>1.1</v>
+        <v>1.265520689700242</v>
       </c>
       <c r="M53" t="n">
-        <v>118</v>
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>24.2798978313</v>
       </c>
     </row>
     <row r="54">
@@ -2943,35 +3104,38 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13.4</v>
+        <v>10.23567805915027</v>
       </c>
       <c r="I54" t="n">
-        <v>4.41</v>
+        <v>3.878921868015809</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.4228451750044744</v>
       </c>
       <c r="K54" t="n">
-        <v>34.9</v>
+        <v>36.48753861741464</v>
       </c>
       <c r="L54" t="n">
-        <v>1.76</v>
+        <v>1.133772668811309</v>
       </c>
       <c r="M54" t="n">
-        <v>4.56</v>
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>12.6343906808</v>
       </c>
     </row>
     <row r="55">
@@ -2990,35 +3154,38 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>19.5</v>
+        <v>16.15843474183713</v>
       </c>
       <c r="I55" t="n">
-        <v>3.91</v>
+        <v>2.447715958396982</v>
       </c>
       <c r="J55" t="n">
-        <v>0.26</v>
+        <v>0.2853508350959969</v>
       </c>
       <c r="K55" t="n">
-        <v>49.4</v>
+        <v>48.55308696081573</v>
       </c>
       <c r="L55" t="n">
-        <v>1.87</v>
+        <v>1.802528474166147</v>
       </c>
       <c r="M55" t="n">
-        <v>1.06</v>
+        <v>1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>137.7383038568</v>
       </c>
     </row>
     <row r="56">
@@ -3037,35 +3204,38 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>4.1</v>
+        <v>14.48031113428612</v>
       </c>
       <c r="I56" t="n">
-        <v>2.54</v>
+        <v>2.150066390627104</v>
       </c>
       <c r="J56" t="n">
-        <v>0.85</v>
+        <v>0.0384156959204033</v>
       </c>
       <c r="K56" t="n">
-        <v>31.8</v>
+        <v>30.24760230585511</v>
       </c>
       <c r="L56" t="n">
-        <v>1.51</v>
+        <v>1.21225892014418</v>
       </c>
       <c r="M56" t="n">
-        <v>166</v>
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>246.3025695129</v>
       </c>
     </row>
     <row r="57">
@@ -3084,35 +3254,38 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>6.7</v>
+        <v>19.08974459050426</v>
       </c>
       <c r="I57" t="n">
-        <v>2.96</v>
+        <v>3.473029244189973</v>
       </c>
       <c r="J57" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1883994642620502</v>
       </c>
       <c r="K57" t="n">
-        <v>41.3</v>
+        <v>40.70411883958053</v>
       </c>
       <c r="L57" t="n">
-        <v>1.28</v>
+        <v>1.49178399530539</v>
       </c>
       <c r="M57" t="n">
-        <v>56.2</v>
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>23.4646336929</v>
       </c>
     </row>
     <row r="58">
@@ -3131,35 +3304,38 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>16</v>
+        <v>11.36102206189426</v>
       </c>
       <c r="I58" t="n">
-        <v>3.67</v>
+        <v>2.803084280498475</v>
       </c>
       <c r="J58" t="n">
-        <v>0.35</v>
+        <v>0.01618754119656434</v>
       </c>
       <c r="K58" t="n">
-        <v>37</v>
+        <v>48.02335561990638</v>
       </c>
       <c r="L58" t="n">
-        <v>1.44</v>
+        <v>1.535286810793287</v>
       </c>
       <c r="M58" t="n">
-        <v>18.3</v>
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>70.0276494089</v>
       </c>
     </row>
     <row r="59">
@@ -3178,35 +3354,38 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>10.4</v>
+        <v>4.091585176314528</v>
       </c>
       <c r="I59" t="n">
-        <v>4.84</v>
+        <v>2.099672678155526</v>
       </c>
       <c r="J59" t="n">
-        <v>0.54</v>
+        <v>0.1491379385152762</v>
       </c>
       <c r="K59" t="n">
-        <v>43.6</v>
+        <v>34.59674433940673</v>
       </c>
       <c r="L59" t="n">
-        <v>1.36</v>
+        <v>1.797737203754483</v>
       </c>
       <c r="M59" t="n">
-        <v>0.391</v>
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>336.7139290617</v>
       </c>
     </row>
     <row r="60">
@@ -3225,35 +3404,38 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.6</v>
+        <v>3.750741175902437</v>
       </c>
       <c r="I60" t="n">
-        <v>2.67</v>
+        <v>4.367462722600763</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1</v>
+        <v>0.9685562504744206</v>
       </c>
       <c r="K60" t="n">
-        <v>39.1</v>
+        <v>46.0504425346822</v>
       </c>
       <c r="L60" t="n">
-        <v>1.97</v>
+        <v>1.23039033172906</v>
       </c>
       <c r="M60" t="n">
-        <v>179</v>
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1.9448223</v>
       </c>
     </row>
     <row r="61">
@@ -3272,35 +3454,38 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>14.5</v>
+        <v>16.53219830570012</v>
       </c>
       <c r="I61" t="n">
-        <v>3.42</v>
+        <v>4.616097093355883</v>
       </c>
       <c r="J61" t="n">
-        <v>0.45</v>
+        <v>0.3943990374556208</v>
       </c>
       <c r="K61" t="n">
-        <v>32</v>
+        <v>38.69691832508746</v>
       </c>
       <c r="L61" t="n">
-        <v>1.64</v>
+        <v>1.971328236668984</v>
       </c>
       <c r="M61" t="n">
-        <v>37.3</v>
+        <v>1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3.0200756397</v>
       </c>
     </row>
   </sheetData>
